--- a/backend/data/financials_by_company/023600.KQ.xlsx
+++ b/backend/data/financials_by_company/023600.KQ.xlsx
@@ -3901,7 +3901,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EE2"/>
+  <dimension ref="A1:ED2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4417,165 +4417,160 @@
       </c>
       <c r="CY1" t="inlineStr">
         <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="CZ1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DJ1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DO1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DP1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="DQ1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="DR1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="DS1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="DT1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
       <c r="ED1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4669,34 +4664,34 @@
         <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>8790</v>
+        <v>8260</v>
       </c>
       <c r="T2" t="n">
-        <v>8750</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>8570</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>8900</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>8790</v>
+        <v>8260</v>
       </c>
       <c r="X2" t="n">
-        <v>8750</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>8570</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>8900</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
         <v>210</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.39</v>
+        <v>2.54</v>
       </c>
       <c r="AC2" t="n">
         <v>1766966400</v>
@@ -4708,28 +4703,28 @@
         <v>2</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.608</v>
+        <v>0.518</v>
       </c>
       <c r="AG2" t="n">
-        <v>12357</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>12357</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>37458</v>
+        <v>36431</v>
       </c>
       <c r="AJ2" t="n">
-        <v>19352</v>
+        <v>14912</v>
       </c>
       <c r="AK2" t="n">
-        <v>19352</v>
+        <v>14912</v>
       </c>
       <c r="AL2" t="n">
-        <v>8650</v>
+        <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>8750</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
@@ -4738,13 +4733,13 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>140072632320</v>
+        <v>137991553024</v>
       </c>
       <c r="AQ2" t="n">
-        <v>140712957000</v>
+        <v>132228558000</v>
       </c>
       <c r="AR2" t="n">
-        <v>8570</v>
+        <v>0</v>
       </c>
       <c r="AS2" t="n">
         <v>11300</v>
@@ -4756,13 +4751,13 @@
         <v>613.5518</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.25787017</v>
+        <v>0.25403893</v>
       </c>
       <c r="AW2" t="n">
-        <v>9711</v>
+        <v>9625.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>9607.1</v>
+        <v>9590.25</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
@@ -4773,7 +4768,7 @@
         <v>0</v>
       </c>
       <c r="BA2" t="n">
-        <v>191293210624</v>
+        <v>189213458432</v>
       </c>
       <c r="BB2" t="n">
         <v>0.0476</v>
@@ -4817,16 +4812,16 @@
         <v>1553731200</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.352</v>
+        <v>0.348</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.545</v>
+        <v>3.507</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-0.042483687</v>
+        <v>-0.16565657</v>
       </c>
       <c r="BR2" t="n">
-        <v>0.27294624</v>
+        <v>0.22635591</v>
       </c>
       <c r="BS2" t="n">
         <v>210</v>
@@ -4840,7 +4835,7 @@
         </is>
       </c>
       <c r="BV2" t="n">
-        <v>8750</v>
+        <v>8620</v>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
@@ -4942,125 +4937,122 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="CY2" t="inlineStr">
+      <c r="CY2" t="n">
+        <v>-1005.5996</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>-0.10447137</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>-970.25</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>-0.10117046</v>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>Sambo Corrugated Board Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="DE2" t="n">
+        <v>4.3583536</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>8620</v>
+      </c>
+      <c r="DG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>950227200000</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>360</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>0.0 - 0.0</t>
+        </is>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="DL2" t="n">
+        <v>36431</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>8620</v>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>0.0 - 11300.0</t>
+        </is>
+      </c>
+      <c r="DO2" t="n">
+        <v>-2680</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>-0.23716815</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-16.565657</v>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DS2" t="n">
+        <v>1780986609</v>
+      </c>
+      <c r="DT2" t="inlineStr">
         <is>
           <t>KOE</t>
         </is>
       </c>
-      <c r="CZ2" t="inlineStr">
+      <c r="DU2" t="inlineStr">
         <is>
           <t>Asia/Seoul</t>
         </is>
       </c>
-      <c r="DA2" t="inlineStr">
+      <c r="DV2" t="inlineStr">
         <is>
           <t>KST</t>
         </is>
       </c>
-      <c r="DB2" t="n">
+      <c r="DW2" t="n">
         <v>32400000</v>
       </c>
-      <c r="DC2" t="inlineStr">
+      <c r="DX2" t="inlineStr">
         <is>
           <t>kr_market</t>
         </is>
       </c>
-      <c r="DD2" t="b">
+      <c r="DY2" t="b">
         <v>0</v>
       </c>
-      <c r="DE2" t="n">
-        <v>-0.45506257</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>8750</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>-961</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>-0.09895994499999999</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>-857.0996</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>-0.089215234</v>
-      </c>
-      <c r="DK2" t="n">
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>SAMBO CORR</t>
+        </is>
+      </c>
+      <c r="EA2" t="n">
         <v>20</v>
       </c>
-      <c r="DL2" t="n">
+      <c r="EB2" t="n">
         <v>20</v>
       </c>
-      <c r="DM2" t="b">
+      <c r="EC2" t="b">
         <v>0</v>
       </c>
-      <c r="DN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>950227200000</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>-40</v>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>8570.0 - 8900.0</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="DS2" t="n">
-        <v>37458</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>180</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>0.021003501</v>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>8570.0 - 11300.0</t>
-        </is>
-      </c>
-      <c r="DW2" t="n">
-        <v>-2550</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-0.22566372</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-4.2483687</v>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="EA2" t="n">
-        <v>1780381828</v>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>SAMBO CORR</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>Sambo Corrugated Board Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr"/>
+      <c r="ED2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
